--- a/Files/Madden25/IE/Season10/ExpectedSalarySheet.xlsx
+++ b/Files/Madden25/IE/Season10/ExpectedSalarySheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenTools/Files/Madden25/IE/Season10/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1963" documentId="13_ncr:1_{76A2A476-6BA5-4945-B1D4-647BCC750DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{630B826B-610F-49F1-84FC-AF35249CD7C0}"/>
+  <xr:revisionPtr revIDLastSave="2226" documentId="13_ncr:1_{76A2A476-6BA5-4945-B1D4-647BCC750DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C52583-FBD7-4D25-93E8-AB75504C3B3B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="225" sheetId="10" r:id="rId1"/>
@@ -20,15 +20,15 @@
     <sheet name="Ratings" sheetId="18" r:id="rId5"/>
     <sheet name="Changes" sheetId="7" r:id="rId6"/>
     <sheet name="Import (Values Only) (255)" sheetId="5" r:id="rId7"/>
-    <sheet name="Import (279) (STANDARD)" sheetId="24" r:id="rId8"/>
-    <sheet name="Import (279) (FA Class)" sheetId="25" r:id="rId9"/>
+    <sheet name="Import (300) (STANDARD)" sheetId="24" r:id="rId8"/>
+    <sheet name="Import (300) (FA Class)" sheetId="25" r:id="rId9"/>
     <sheet name="Cap" sheetId="11" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'225'!$A$1:$AA$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'255'!$A$1:$AA$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Import (279) (FA Class)'!$A$1:$M$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Import (279) (STANDARD)'!$A$1:$M$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Import (300) (FA Class)'!$A$1:$M$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Import (300) (STANDARD)'!$A$1:$M$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="51">
   <si>
     <t>int0</t>
   </si>
@@ -198,6 +198,9 @@
   <si>
     <t>HB</t>
   </si>
+  <si>
+    <t>LS</t>
+  </si>
 </sst>
 </file>
 
@@ -271,6 +274,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -62889,7 +62896,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7C77F9-E84A-49EE-987B-BFA5EFE6C6B7}">
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="13" width="12.875" style="4" customWidth="1"/>
@@ -62946,7 +62953,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2">
         <v>65</v>
@@ -62991,10 +62998,10 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C3" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D3" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E3" s="2">
         <v>400</v>
@@ -63003,13 +63010,13 @@
         <v>800</v>
       </c>
       <c r="G3" s="2">
-        <v>1050</v>
+        <v>1350</v>
       </c>
       <c r="H3" s="2">
         <v>3350</v>
       </c>
       <c r="I3" s="2">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="J3" s="2">
         <v>5300</v>
@@ -63018,7 +63025,7 @@
         <v>5500</v>
       </c>
       <c r="L3" s="2">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>11</v>
@@ -63035,7 +63042,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2">
         <v>150</v>
@@ -63079,10 +63086,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>2</v>
@@ -63126,10 +63133,10 @@
         <v>70</v>
       </c>
       <c r="G6" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" s="2">
         <v>77</v>
@@ -63164,25 +63171,25 @@
         <v>110</v>
       </c>
       <c r="F7" s="2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G7" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H7" s="2">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="I7" s="2">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="J7" s="2">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="K7" s="2">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="L7" s="2">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>49</v>
@@ -63205,22 +63212,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="I8" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J8" s="2">
         <v>250</v>
       </c>
       <c r="K8" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L8" s="2">
         <v>450</v>
@@ -63255,7 +63262,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2">
         <v>3</v>
@@ -63299,7 +63306,7 @@
         <v>74</v>
       </c>
       <c r="J10" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K10" s="2">
         <v>80</v>
@@ -63331,22 +63338,22 @@
         <v>98.460000000000008</v>
       </c>
       <c r="G11" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2">
         <v>120.34</v>
       </c>
       <c r="I11" s="2">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="J11" s="2">
         <v>200</v>
       </c>
       <c r="K11" s="2">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="L11" s="2">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>13</v>
@@ -63451,7 +63458,7 @@
         <v>68</v>
       </c>
       <c r="F14" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2">
         <v>75</v>
@@ -63466,10 +63473,10 @@
         <v>84</v>
       </c>
       <c r="K14" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L14" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>14</v>
@@ -63486,31 +63493,31 @@
         <v>98.460000000000008</v>
       </c>
       <c r="D15" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F15" s="2">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="G15" s="2">
-        <v>525</v>
+        <v>850</v>
       </c>
       <c r="H15" s="2">
-        <v>1200</v>
+        <v>1450</v>
       </c>
       <c r="I15" s="2">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="J15" s="2">
-        <v>2500</v>
+        <v>2750</v>
       </c>
       <c r="K15" s="2">
-        <v>3000</v>
+        <v>3250</v>
       </c>
       <c r="L15" s="2">
-        <v>4000</v>
+        <v>4250</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>14</v>
@@ -63533,13 +63540,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="G16" s="2">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="H16" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I16" s="2">
         <v>400</v>
@@ -63551,7 +63558,7 @@
         <v>650</v>
       </c>
       <c r="L16" s="2">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>14</v>
@@ -63609,13 +63616,13 @@
         <v>64</v>
       </c>
       <c r="D18" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F18" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2">
         <v>73</v>
@@ -63624,7 +63631,7 @@
         <v>75</v>
       </c>
       <c r="I18" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J18" s="2">
         <v>85</v>
@@ -63647,34 +63654,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C19" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F19" s="2">
         <v>600</v>
       </c>
       <c r="G19" s="2">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="H19" s="2">
         <v>900</v>
       </c>
       <c r="I19" s="2">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="J19" s="2">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="K19" s="2">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="L19" s="2">
-        <v>1950</v>
+        <v>1900</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>15</v>
@@ -63694,16 +63701,16 @@
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F20" s="2">
         <v>170</v>
       </c>
       <c r="G20" s="2">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H20" s="2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="I20" s="2">
         <v>270</v>
@@ -63788,7 +63795,7 @@
         <v>74</v>
       </c>
       <c r="I22" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J22" s="2">
         <v>80</v>
@@ -63820,22 +63827,22 @@
         <v>200</v>
       </c>
       <c r="F23" s="2">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G23" s="2">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="H23" s="2">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I23" s="2">
-        <v>1600</v>
+        <v>1950</v>
       </c>
       <c r="J23" s="2">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="K23" s="2">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="L23" s="2">
         <v>3000</v>
@@ -63864,7 +63871,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="2">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H24" s="2">
         <v>350</v>
@@ -63876,10 +63883,10 @@
         <v>500</v>
       </c>
       <c r="K24" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="L24" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>16</v>
@@ -63958,7 +63965,7 @@
         <v>80</v>
       </c>
       <c r="K26" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L26" s="2">
         <v>95</v>
@@ -63990,7 +63997,7 @@
         <v>500</v>
       </c>
       <c r="H27" s="2">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I27" s="2">
         <v>1100</v>
@@ -64002,7 +64009,7 @@
         <v>2000</v>
       </c>
       <c r="L27" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>17</v>
@@ -64125,7 +64132,7 @@
         <v>90</v>
       </c>
       <c r="L30" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>18</v>
@@ -64157,7 +64164,7 @@
         <v>700</v>
       </c>
       <c r="I31" s="2">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J31" s="2">
         <v>1200</v>
@@ -64166,7 +64173,7 @@
         <v>1700</v>
       </c>
       <c r="L31" s="2">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>18</v>
@@ -64201,7 +64208,7 @@
         <v>200</v>
       </c>
       <c r="J32" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="K32" s="2">
         <v>400</v>
@@ -64286,7 +64293,7 @@
         <v>80</v>
       </c>
       <c r="K34" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L34" s="2">
         <v>95</v>
@@ -64318,7 +64325,7 @@
         <v>500</v>
       </c>
       <c r="H35" s="2">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I35" s="2">
         <v>1100</v>
@@ -64330,7 +64337,7 @@
         <v>2000</v>
       </c>
       <c r="L35" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>19</v>
@@ -64444,7 +64451,7 @@
         <v>74</v>
       </c>
       <c r="I38" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J38" s="2">
         <v>80</v>
@@ -64479,22 +64486,22 @@
         <v>350</v>
       </c>
       <c r="G39" s="2">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="H39" s="2">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="I39" s="2">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="J39" s="2">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="K39" s="2">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="L39" s="2">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>20</v>
@@ -64602,22 +64609,22 @@
         <v>70</v>
       </c>
       <c r="G42" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H42" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I42" s="2">
         <v>80</v>
       </c>
       <c r="J42" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K42" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L42" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>21</v>
@@ -64631,34 +64638,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C43" s="2">
-        <v>98.460000000000008</v>
+        <v>100</v>
       </c>
       <c r="D43" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E43" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F43" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G43" s="2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H43" s="2">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I43" s="2">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="J43" s="2">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="K43" s="2">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="L43" s="2">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>21</v>
@@ -64684,10 +64691,10 @@
         <v>150</v>
       </c>
       <c r="G44" s="2">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="H44" s="2">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="I44" s="2">
         <v>450</v>
@@ -64696,10 +64703,10 @@
         <v>500</v>
       </c>
       <c r="K44" s="2">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="L44" s="2">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>21</v>
@@ -64740,7 +64747,7 @@
         <v>4</v>
       </c>
       <c r="L45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>21</v>
@@ -64766,22 +64773,22 @@
         <v>70</v>
       </c>
       <c r="G46" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H46" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I46" s="2">
         <v>80</v>
       </c>
       <c r="J46" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K46" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L46" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>22</v>
@@ -64795,34 +64802,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C47" s="2">
-        <v>98.460000000000008</v>
+        <v>100</v>
       </c>
       <c r="D47" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E47" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F47" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G47" s="2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H47" s="2">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I47" s="2">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="J47" s="2">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="K47" s="2">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="L47" s="2">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>22</v>
@@ -64848,10 +64855,10 @@
         <v>150</v>
       </c>
       <c r="G48" s="2">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="H48" s="2">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="I48" s="2">
         <v>450</v>
@@ -64860,10 +64867,10 @@
         <v>500</v>
       </c>
       <c r="K48" s="2">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="L48" s="2">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>22</v>
@@ -64904,7 +64911,7 @@
         <v>4</v>
       </c>
       <c r="L49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>22</v>
@@ -64930,10 +64937,10 @@
         <v>70</v>
       </c>
       <c r="G50" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H50" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I50" s="2">
         <v>80</v>
@@ -64945,7 +64952,7 @@
         <v>87</v>
       </c>
       <c r="L50" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>23</v>
@@ -64959,34 +64966,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C51" s="2">
-        <v>98.460000000000008</v>
+        <v>100</v>
       </c>
       <c r="D51" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E51" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F51" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G51" s="2">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H51" s="2">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="I51" s="2">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="J51" s="2">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="K51" s="2">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="L51" s="2">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>23</v>
@@ -65012,13 +65019,13 @@
         <v>120</v>
       </c>
       <c r="G52" s="2">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="H52" s="2">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="I52" s="2">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="J52" s="2">
         <v>450</v>
@@ -65141,7 +65148,7 @@
         <v>600</v>
       </c>
       <c r="I55" s="2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J55" s="2">
         <v>1500</v>
@@ -65150,7 +65157,7 @@
         <v>1800</v>
       </c>
       <c r="L55" s="2">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>24</v>
@@ -65299,13 +65306,13 @@
         <v>160</v>
       </c>
       <c r="G59" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H59" s="2">
         <v>700</v>
       </c>
       <c r="I59" s="2">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J59" s="2">
         <v>1500</v>
@@ -65469,7 +65476,7 @@
         <v>600</v>
       </c>
       <c r="I63" s="2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J63" s="2">
         <v>1500</v>
@@ -65478,7 +65485,7 @@
         <v>1800</v>
       </c>
       <c r="L63" s="2">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>26</v>
@@ -65601,7 +65608,7 @@
         <v>90</v>
       </c>
       <c r="L66" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>27</v>
@@ -65624,22 +65631,22 @@
         <v>120</v>
       </c>
       <c r="F67" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G67" s="2">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="H67" s="2">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="I67" s="2">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="J67" s="2">
-        <v>1900</v>
+        <v>2250</v>
       </c>
       <c r="K67" s="2">
-        <v>2400</v>
+        <v>2750</v>
       </c>
       <c r="L67" s="2">
         <v>3000</v>
@@ -65665,19 +65672,19 @@
         <v>0</v>
       </c>
       <c r="F68" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G68" s="2">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H68" s="2">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="I68" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="J68" s="2">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K68" s="2">
         <v>500</v>
@@ -65759,13 +65766,13 @@
         <v>80</v>
       </c>
       <c r="J70" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K70" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L70" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>28</v>
@@ -65794,19 +65801,19 @@
         <v>300</v>
       </c>
       <c r="H71" s="2">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I71" s="2">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="J71" s="2">
         <v>1500</v>
       </c>
       <c r="K71" s="2">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="L71" s="2">
-        <v>2150</v>
+        <v>2500</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>28</v>
@@ -65923,13 +65930,13 @@
         <v>80</v>
       </c>
       <c r="J74" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K74" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L74" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M74" s="5" t="s">
         <v>29</v>
@@ -65958,19 +65965,19 @@
         <v>300</v>
       </c>
       <c r="H75" s="2">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I75" s="2">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="J75" s="2">
         <v>1500</v>
       </c>
       <c r="K75" s="2">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="L75" s="2">
-        <v>2150</v>
+        <v>2500</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>29</v>
@@ -66116,25 +66123,25 @@
         <v>109.4</v>
       </c>
       <c r="F79" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G79" s="2">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="H79" s="2">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="I79" s="2">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="J79" s="2">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="K79" s="2">
         <v>550</v>
       </c>
       <c r="L79" s="2">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>30</v>
@@ -66280,22 +66287,22 @@
         <v>109.4</v>
       </c>
       <c r="F83" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G83" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H83" s="2">
         <v>250</v>
       </c>
       <c r="I83" s="2">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="J83" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K83" s="2">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="L83" s="2">
         <v>400</v>
@@ -66333,10 +66340,10 @@
         <v>70</v>
       </c>
       <c r="J84" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K84" s="2">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L84" s="2">
         <v>150</v>
@@ -66384,6 +66391,170 @@
       </c>
       <c r="M85" s="5" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>44</v>
+      </c>
+      <c r="B86">
+        <v>58</v>
+      </c>
+      <c r="C86">
+        <v>60</v>
+      </c>
+      <c r="D86">
+        <v>62</v>
+      </c>
+      <c r="E86">
+        <v>63</v>
+      </c>
+      <c r="F86">
+        <v>64</v>
+      </c>
+      <c r="G86">
+        <v>65</v>
+      </c>
+      <c r="H86">
+        <v>68</v>
+      </c>
+      <c r="I86">
+        <v>70</v>
+      </c>
+      <c r="J86">
+        <v>72</v>
+      </c>
+      <c r="K86">
+        <v>77</v>
+      </c>
+      <c r="L86">
+        <v>80</v>
+      </c>
+      <c r="M86" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87">
+        <v>98</v>
+      </c>
+      <c r="C87">
+        <v>98</v>
+      </c>
+      <c r="D87">
+        <v>100</v>
+      </c>
+      <c r="E87">
+        <v>100</v>
+      </c>
+      <c r="F87">
+        <v>100</v>
+      </c>
+      <c r="G87">
+        <v>110</v>
+      </c>
+      <c r="H87">
+        <v>125</v>
+      </c>
+      <c r="I87">
+        <v>141</v>
+      </c>
+      <c r="J87">
+        <v>147</v>
+      </c>
+      <c r="K87">
+        <v>162</v>
+      </c>
+      <c r="L87">
+        <v>165</v>
+      </c>
+      <c r="M87" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>5</v>
+      </c>
+      <c r="H88">
+        <v>10</v>
+      </c>
+      <c r="I88">
+        <v>15</v>
+      </c>
+      <c r="J88">
+        <v>20</v>
+      </c>
+      <c r="K88">
+        <v>25</v>
+      </c>
+      <c r="L88">
+        <v>30</v>
+      </c>
+      <c r="M88" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>46</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89">
+        <v>2</v>
+      </c>
+      <c r="J89">
+        <v>3</v>
+      </c>
+      <c r="K89">
+        <v>3</v>
+      </c>
+      <c r="L89">
+        <v>4</v>
+      </c>
+      <c r="M89" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -66394,7 +66565,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D12E5A2B-9604-4357-AFE7-3C2141D21BC3}">
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="13" width="12.875" style="4" customWidth="1"/>
@@ -66451,7 +66622,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="2">
         <v>65</v>
@@ -66496,10 +66667,10 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C3" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D3" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="E3" s="2">
         <v>400</v>
@@ -66508,13 +66679,13 @@
         <v>800</v>
       </c>
       <c r="G3" s="2">
-        <v>1050</v>
+        <v>1350</v>
       </c>
       <c r="H3" s="2">
         <v>3350</v>
       </c>
       <c r="I3" s="2">
-        <v>4300</v>
+        <v>4500</v>
       </c>
       <c r="J3" s="2">
         <v>5300</v>
@@ -66523,7 +66694,7 @@
         <v>5500</v>
       </c>
       <c r="L3" s="2">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>11</v>
@@ -66540,7 +66711,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2">
         <v>150</v>
@@ -66584,10 +66755,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>2</v>
@@ -66631,10 +66802,10 @@
         <v>70</v>
       </c>
       <c r="G6" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" s="2">
         <v>77</v>
@@ -66669,25 +66840,25 @@
         <v>110</v>
       </c>
       <c r="F7" s="2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G7" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H7" s="2">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="I7" s="2">
-        <v>600</v>
+        <v>750</v>
       </c>
       <c r="J7" s="2">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="K7" s="2">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="L7" s="2">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>49</v>
@@ -66710,22 +66881,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="I8" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J8" s="2">
         <v>250</v>
       </c>
       <c r="K8" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L8" s="2">
         <v>450</v>
@@ -66760,7 +66931,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="2">
         <v>3</v>
@@ -66804,7 +66975,7 @@
         <v>74</v>
       </c>
       <c r="J10" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K10" s="2">
         <v>80</v>
@@ -66836,22 +67007,22 @@
         <v>98.460000000000008</v>
       </c>
       <c r="G11" s="2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2">
         <v>120.34</v>
       </c>
       <c r="I11" s="2">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="J11" s="2">
         <v>200</v>
       </c>
       <c r="K11" s="2">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="L11" s="2">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>13</v>
@@ -66956,16 +67127,16 @@
         <v>68</v>
       </c>
       <c r="F14" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2">
         <v>75</v>
       </c>
       <c r="H14" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I14" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J14" s="2">
         <v>83</v>
@@ -66974,7 +67145,7 @@
         <v>88</v>
       </c>
       <c r="L14" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>14</v>
@@ -66991,31 +67162,31 @@
         <v>98.460000000000008</v>
       </c>
       <c r="D15" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E15" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F15" s="2">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="G15" s="2">
-        <v>525</v>
+        <v>850</v>
       </c>
       <c r="H15" s="2">
-        <v>1200</v>
+        <v>1450</v>
       </c>
       <c r="I15" s="2">
-        <v>1500</v>
+        <v>1750</v>
       </c>
       <c r="J15" s="2">
-        <v>2500</v>
+        <v>2750</v>
       </c>
       <c r="K15" s="2">
-        <v>3000</v>
+        <v>3250</v>
       </c>
       <c r="L15" s="2">
-        <v>4000</v>
+        <v>4250</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>14</v>
@@ -67038,13 +67209,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="G16" s="2">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="H16" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I16" s="2">
         <v>400</v>
@@ -67056,7 +67227,7 @@
         <v>650</v>
       </c>
       <c r="L16" s="2">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>14</v>
@@ -67114,13 +67285,13 @@
         <v>64</v>
       </c>
       <c r="D18" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F18" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2">
         <v>73</v>
@@ -67129,10 +67300,10 @@
         <v>75</v>
       </c>
       <c r="I18" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J18" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K18" s="2">
         <v>90</v>
@@ -67152,34 +67323,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C19" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="E19" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F19" s="2">
         <v>600</v>
       </c>
       <c r="G19" s="2">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="H19" s="2">
         <v>900</v>
       </c>
       <c r="I19" s="2">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J19" s="2">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="K19" s="2">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="L19" s="2">
-        <v>1950</v>
+        <v>1900</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>15</v>
@@ -67199,19 +67370,19 @@
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="F20" s="2">
         <v>170</v>
       </c>
       <c r="G20" s="2">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="H20" s="2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="I20" s="2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="J20" s="2">
         <v>300</v>
@@ -67293,13 +67464,13 @@
         <v>74</v>
       </c>
       <c r="I22" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J22" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K22" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L22" s="2">
         <v>95</v>
@@ -67325,22 +67496,22 @@
         <v>200</v>
       </c>
       <c r="F23" s="2">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G23" s="2">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="H23" s="2">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I23" s="2">
-        <v>1600</v>
+        <v>1950</v>
       </c>
       <c r="J23" s="2">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="K23" s="2">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="L23" s="2">
         <v>3000</v>
@@ -67369,7 +67540,7 @@
         <v>100</v>
       </c>
       <c r="G24" s="2">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="H24" s="2">
         <v>350</v>
@@ -67381,10 +67552,10 @@
         <v>500</v>
       </c>
       <c r="K24" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="L24" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>16</v>
@@ -67454,19 +67625,19 @@
         <v>70</v>
       </c>
       <c r="H26" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I26" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J26" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K26" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L26" s="2">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>17</v>
@@ -67495,7 +67666,7 @@
         <v>500</v>
       </c>
       <c r="H27" s="2">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I27" s="2">
         <v>1100</v>
@@ -67507,7 +67678,7 @@
         <v>2000</v>
       </c>
       <c r="L27" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>17</v>
@@ -67618,7 +67789,7 @@
         <v>70</v>
       </c>
       <c r="H30" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I30" s="2">
         <v>76</v>
@@ -67627,10 +67798,10 @@
         <v>80</v>
       </c>
       <c r="K30" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L30" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>18</v>
@@ -67662,7 +67833,7 @@
         <v>700</v>
       </c>
       <c r="I31" s="2">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="J31" s="2">
         <v>1200</v>
@@ -67671,7 +67842,7 @@
         <v>1700</v>
       </c>
       <c r="L31" s="2">
-        <v>1900</v>
+        <v>2500</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>18</v>
@@ -67706,7 +67877,7 @@
         <v>200</v>
       </c>
       <c r="J32" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="K32" s="2">
         <v>400</v>
@@ -67782,19 +67953,19 @@
         <v>70</v>
       </c>
       <c r="H34" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I34" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J34" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K34" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="L34" s="2">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>19</v>
@@ -67823,7 +67994,7 @@
         <v>500</v>
       </c>
       <c r="H35" s="2">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I35" s="2">
         <v>1100</v>
@@ -67835,7 +68006,7 @@
         <v>2000</v>
       </c>
       <c r="L35" s="2">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>19</v>
@@ -67949,13 +68120,13 @@
         <v>74</v>
       </c>
       <c r="I38" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J38" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K38" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L38" s="2">
         <v>95</v>
@@ -67984,22 +68155,22 @@
         <v>350</v>
       </c>
       <c r="G39" s="2">
-        <v>850</v>
+        <v>700</v>
       </c>
       <c r="H39" s="2">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="I39" s="2">
-        <v>1450</v>
+        <v>1500</v>
       </c>
       <c r="J39" s="2">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="K39" s="2">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="L39" s="2">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>20</v>
@@ -68107,22 +68278,22 @@
         <v>70</v>
       </c>
       <c r="G42" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H42" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I42" s="2">
         <v>80</v>
       </c>
       <c r="J42" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K42" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L42" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>21</v>
@@ -68136,34 +68307,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C43" s="2">
-        <v>98.460000000000008</v>
+        <v>100</v>
       </c>
       <c r="D43" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E43" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F43" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G43" s="2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H43" s="2">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I43" s="2">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="J43" s="2">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="K43" s="2">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="L43" s="2">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>21</v>
@@ -68189,10 +68360,10 @@
         <v>150</v>
       </c>
       <c r="G44" s="2">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="H44" s="2">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="I44" s="2">
         <v>450</v>
@@ -68201,10 +68372,10 @@
         <v>500</v>
       </c>
       <c r="K44" s="2">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="L44" s="2">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>21</v>
@@ -68245,7 +68416,7 @@
         <v>4</v>
       </c>
       <c r="L45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>21</v>
@@ -68271,22 +68442,22 @@
         <v>70</v>
       </c>
       <c r="G46" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H46" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I46" s="2">
         <v>80</v>
       </c>
       <c r="J46" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K46" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L46" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>22</v>
@@ -68300,34 +68471,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C47" s="2">
-        <v>98.460000000000008</v>
+        <v>100</v>
       </c>
       <c r="D47" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E47" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F47" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G47" s="2">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H47" s="2">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I47" s="2">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="J47" s="2">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="K47" s="2">
-        <v>2800</v>
+        <v>3600</v>
       </c>
       <c r="L47" s="2">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>22</v>
@@ -68353,10 +68524,10 @@
         <v>150</v>
       </c>
       <c r="G48" s="2">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="H48" s="2">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="I48" s="2">
         <v>450</v>
@@ -68365,10 +68536,10 @@
         <v>500</v>
       </c>
       <c r="K48" s="2">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="L48" s="2">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>22</v>
@@ -68409,7 +68580,7 @@
         <v>4</v>
       </c>
       <c r="L49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>22</v>
@@ -68435,19 +68606,19 @@
         <v>70</v>
       </c>
       <c r="G50" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H50" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I50" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J50" s="2">
+        <v>83</v>
+      </c>
+      <c r="K50" s="2">
         <v>85</v>
-      </c>
-      <c r="K50" s="2">
-        <v>87</v>
       </c>
       <c r="L50" s="2">
         <v>95</v>
@@ -68464,34 +68635,34 @@
         <v>98.460000000000008</v>
       </c>
       <c r="C51" s="2">
-        <v>98.460000000000008</v>
+        <v>100</v>
       </c>
       <c r="D51" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E51" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F51" s="2">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G51" s="2">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H51" s="2">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="I51" s="2">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="J51" s="2">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="K51" s="2">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="L51" s="2">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>23</v>
@@ -68517,13 +68688,13 @@
         <v>120</v>
       </c>
       <c r="G52" s="2">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="H52" s="2">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="I52" s="2">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="J52" s="2">
         <v>450</v>
@@ -68605,16 +68776,16 @@
         <v>75</v>
       </c>
       <c r="I54" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J54" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K54" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L54" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>24</v>
@@ -68646,7 +68817,7 @@
         <v>600</v>
       </c>
       <c r="I55" s="2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J55" s="2">
         <v>1500</v>
@@ -68655,7 +68826,7 @@
         <v>1800</v>
       </c>
       <c r="L55" s="2">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>24</v>
@@ -68769,16 +68940,16 @@
         <v>75</v>
       </c>
       <c r="I58" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J58" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K58" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L58" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>25</v>
@@ -68804,13 +68975,13 @@
         <v>160</v>
       </c>
       <c r="G59" s="2">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H59" s="2">
         <v>700</v>
       </c>
       <c r="I59" s="2">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="J59" s="2">
         <v>1500</v>
@@ -68933,16 +69104,16 @@
         <v>75</v>
       </c>
       <c r="I62" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J62" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K62" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="L62" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>26</v>
@@ -68974,7 +69145,7 @@
         <v>600</v>
       </c>
       <c r="I63" s="2">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J63" s="2">
         <v>1500</v>
@@ -68983,7 +69154,7 @@
         <v>1800</v>
       </c>
       <c r="L63" s="2">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>26</v>
@@ -69094,19 +69265,19 @@
         <v>74</v>
       </c>
       <c r="H66" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I66" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J66" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K66" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L66" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>27</v>
@@ -69129,22 +69300,22 @@
         <v>120</v>
       </c>
       <c r="F67" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G67" s="2">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="H67" s="2">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="I67" s="2">
-        <v>1000</v>
+        <v>1750</v>
       </c>
       <c r="J67" s="2">
-        <v>1900</v>
+        <v>2250</v>
       </c>
       <c r="K67" s="2">
-        <v>2400</v>
+        <v>2750</v>
       </c>
       <c r="L67" s="2">
         <v>3000</v>
@@ -69170,19 +69341,19 @@
         <v>0</v>
       </c>
       <c r="F68" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G68" s="2">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="H68" s="2">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="I68" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="J68" s="2">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K68" s="2">
         <v>500</v>
@@ -69264,13 +69435,13 @@
         <v>80</v>
       </c>
       <c r="J70" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K70" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L70" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>28</v>
@@ -69299,19 +69470,19 @@
         <v>300</v>
       </c>
       <c r="H71" s="2">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I71" s="2">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="J71" s="2">
         <v>1500</v>
       </c>
       <c r="K71" s="2">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="L71" s="2">
-        <v>2150</v>
+        <v>2500</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>28</v>
@@ -69428,13 +69599,13 @@
         <v>80</v>
       </c>
       <c r="J74" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K74" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L74" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M74" s="5" t="s">
         <v>29</v>
@@ -69463,19 +69634,19 @@
         <v>300</v>
       </c>
       <c r="H75" s="2">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I75" s="2">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="J75" s="2">
         <v>1500</v>
       </c>
       <c r="K75" s="2">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="L75" s="2">
-        <v>2150</v>
+        <v>2500</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>29</v>
@@ -69621,25 +69792,25 @@
         <v>109.4</v>
       </c>
       <c r="F79" s="2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G79" s="2">
-        <v>360</v>
+        <v>250</v>
       </c>
       <c r="H79" s="2">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="I79" s="2">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="J79" s="2">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="K79" s="2">
         <v>550</v>
       </c>
       <c r="L79" s="2">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>30</v>
@@ -69785,22 +69956,22 @@
         <v>109.4</v>
       </c>
       <c r="F83" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G83" s="2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H83" s="2">
         <v>250</v>
       </c>
       <c r="I83" s="2">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="J83" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="K83" s="2">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="L83" s="2">
         <v>400</v>
@@ -69838,10 +70009,10 @@
         <v>70</v>
       </c>
       <c r="J84" s="2">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K84" s="2">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L84" s="2">
         <v>150</v>
@@ -69889,6 +70060,170 @@
       </c>
       <c r="M85" s="5" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>44</v>
+      </c>
+      <c r="B86">
+        <v>58</v>
+      </c>
+      <c r="C86">
+        <v>60</v>
+      </c>
+      <c r="D86">
+        <v>62</v>
+      </c>
+      <c r="E86">
+        <v>63</v>
+      </c>
+      <c r="F86">
+        <v>64</v>
+      </c>
+      <c r="G86">
+        <v>65</v>
+      </c>
+      <c r="H86">
+        <v>68</v>
+      </c>
+      <c r="I86">
+        <v>70</v>
+      </c>
+      <c r="J86">
+        <v>72</v>
+      </c>
+      <c r="K86">
+        <v>77</v>
+      </c>
+      <c r="L86">
+        <v>80</v>
+      </c>
+      <c r="M86" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87">
+        <v>98</v>
+      </c>
+      <c r="C87">
+        <v>98</v>
+      </c>
+      <c r="D87">
+        <v>100</v>
+      </c>
+      <c r="E87">
+        <v>100</v>
+      </c>
+      <c r="F87">
+        <v>100</v>
+      </c>
+      <c r="G87">
+        <v>110</v>
+      </c>
+      <c r="H87">
+        <v>125</v>
+      </c>
+      <c r="I87">
+        <v>141</v>
+      </c>
+      <c r="J87">
+        <v>147</v>
+      </c>
+      <c r="K87">
+        <v>162</v>
+      </c>
+      <c r="L87">
+        <v>165</v>
+      </c>
+      <c r="M87" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>5</v>
+      </c>
+      <c r="H88">
+        <v>10</v>
+      </c>
+      <c r="I88">
+        <v>15</v>
+      </c>
+      <c r="J88">
+        <v>20</v>
+      </c>
+      <c r="K88">
+        <v>25</v>
+      </c>
+      <c r="L88">
+        <v>30</v>
+      </c>
+      <c r="M88" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>46</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89">
+        <v>2</v>
+      </c>
+      <c r="J89">
+        <v>3</v>
+      </c>
+      <c r="K89">
+        <v>3</v>
+      </c>
+      <c r="L89">
+        <v>4</v>
+      </c>
+      <c r="M89" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
